--- a/Excel/城市.xlsx
+++ b/Excel/城市.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\exeProject\ideaProjects\Project-HaiFeng\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F81EA58F-B625-44B5-98C3-36C1EC05A1D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AC87BD7-E4A3-4F75-B139-394263B9D3C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" firstSheet="10" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="21820" windowHeight="13900" firstSheet="8" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="城市主表" sheetId="1" r:id="rId1"/>
@@ -29,13 +29,14 @@
     <sheet name="住房政策" sheetId="14" r:id="rId14"/>
     <sheet name="租房成本" sheetId="15" r:id="rId15"/>
     <sheet name="注意事项" sheetId="16" r:id="rId16"/>
+    <sheet name="Sheet1" sheetId="17" r:id="rId17"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="652" uniqueCount="189">
   <si>
     <t>城市名称</t>
   </si>
@@ -575,6 +576,42 @@
   </si>
   <si>
     <t>注：Sheet1~13为JSONB字段，数据库无精度限制，代码自动过滤null值</t>
+  </si>
+  <si>
+    <t>城市名称</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>产业描述</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>String</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>STRING</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">主要产业(逗号分隔) </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">新兴产业(逗号分隔) </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>中英文逗号均可分隔</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>无长度限制</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Text[]</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -593,6 +630,7 @@
       <b/>
       <sz val="11"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -603,7 +641,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -622,6 +660,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FF00B050"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -635,13 +685,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -946,6 +1000,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H1"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="13.36328125" customWidth="1"/>
+    <col min="6" max="6" width="14.26953125" customWidth="1"/>
+    <col min="7" max="7" width="15.90625" customWidth="1"/>
+    <col min="8" max="8" width="18.6328125" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -1387,7 +1447,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>96</v>
       </c>
@@ -1404,7 +1464,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>0</v>
       </c>
@@ -1421,7 +1481,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>8</v>
       </c>
@@ -1435,7 +1495,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>9</v>
       </c>
@@ -1449,7 +1509,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>10</v>
       </c>
@@ -1463,7 +1523,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>11</v>
       </c>
@@ -1477,7 +1537,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>12</v>
       </c>
@@ -1491,7 +1551,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>13</v>
       </c>
@@ -1505,7 +1565,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>14</v>
       </c>
@@ -1519,7 +1579,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>15</v>
       </c>
@@ -1533,7 +1593,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>16</v>
       </c>
@@ -1547,7 +1607,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>17</v>
       </c>
@@ -1561,7 +1621,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>18</v>
       </c>
@@ -1575,24 +1635,75 @@
         <v>178</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>181</v>
+      </c>
+      <c r="B46" t="s">
+        <v>182</v>
+      </c>
+      <c r="C46" t="s">
+        <v>106</v>
+      </c>
+      <c r="D46" t="s">
+        <v>183</v>
+      </c>
+      <c r="E46" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>184</v>
+      </c>
+      <c r="B47" t="s">
+        <v>188</v>
+      </c>
+      <c r="C47" t="s">
+        <v>106</v>
+      </c>
+      <c r="D47" t="s">
+        <v>183</v>
+      </c>
+      <c r="E47" s="4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>185</v>
+      </c>
+      <c r="B48" t="s">
+        <v>188</v>
+      </c>
+      <c r="C48" t="s">
+        <v>106</v>
+      </c>
+      <c r="D48" t="s">
+        <v>183</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="B46" s="3"/>
-      <c r="C46" s="3"/>
-      <c r="D46" s="3"/>
-      <c r="E46" s="3"/>
-      <c r="F46" s="3"/>
-      <c r="G46" s="3"/>
-      <c r="H46" s="3"/>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B50" s="3"/>
+      <c r="C50" s="3"/>
+      <c r="D50" s="3"/>
+      <c r="E50" s="3"/>
+      <c r="F50" s="3"/>
+      <c r="G50" s="3"/>
+      <c r="H50" s="3"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>96</v>
       </c>
@@ -1609,7 +1720,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>0</v>
       </c>
@@ -1626,7 +1737,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>22</v>
       </c>
@@ -1643,7 +1754,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>23</v>
       </c>
@@ -1660,7 +1771,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>24</v>
       </c>
@@ -1677,12 +1788,12 @@
         <v>110</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>96</v>
       </c>
@@ -1699,7 +1810,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>0</v>
       </c>
@@ -1716,7 +1827,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>25</v>
       </c>
@@ -1730,7 +1841,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>26</v>
       </c>
@@ -1744,7 +1855,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>27</v>
       </c>
@@ -1761,7 +1872,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>28</v>
       </c>
@@ -1775,7 +1886,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>29</v>
       </c>
@@ -2976,7 +3087,7 @@
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="B155" t="s">
         <v>101</v>
@@ -3116,6 +3227,16 @@
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F82A739-9524-4489-BDC5-3D2179160EB6}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -3123,6 +3244,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:O1"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="15.90625" customWidth="1"/>
+    <col min="5" max="5" width="18.36328125" customWidth="1"/>
+    <col min="6" max="6" width="20.6328125" customWidth="1"/>
+    <col min="7" max="7" width="13.7265625" customWidth="1"/>
+    <col min="8" max="8" width="18.36328125" customWidth="1"/>
+    <col min="9" max="9" width="12.453125" customWidth="1"/>
+    <col min="10" max="10" width="15.453125" customWidth="1"/>
+    <col min="11" max="11" width="14.1796875" customWidth="1"/>
+    <col min="12" max="12" width="19.36328125" customWidth="1"/>
+    <col min="13" max="13" width="11.453125" customWidth="1"/>
+    <col min="14" max="14" width="18.26953125" customWidth="1"/>
+    <col min="15" max="15" width="17.1796875" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -3164,10 +3299,10 @@
       <c r="M1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="N1" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="5" t="s">
         <v>21</v>
       </c>
     </row>
